--- a/public/data/ARVO_카드샵_DB_한국_일본_2026-09-11.xlsx
+++ b/public/data/ARVO_카드샵_DB_한국_일본_2026-09-11.xlsx
@@ -1230,18 +1230,30 @@
       </c>
       <c r="L5" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M5" s="178" t="n"/>
-      <c r="N5" s="178" t="n"/>
-      <c r="O5" s="178" t="n"/>
+          <t>@cardstory.tcg</t>
+        </is>
+      </c>
+      <c r="M5" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cardstory.tcg/</t>
+        </is>
+      </c>
+      <c r="N5" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/775524702_17936546637347019_4392681646294703985_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=Iw0WdPHJTd8Q7kNvwF2nK29&amp;_nc_oc=AdrxHXUGqorSShnzcdXGZMWXbs1ovU6xhdFLEBtEgLmBXdD-cHTZTlYQk-JW1OX4jBk&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=7ClEtXxmr94b-q5IPTwhxw&amp;_nc_ss=7fa02&amp;oh=00_AQKtCEq_0PDFEeVi1pMgwfAMSh4rNXKXSE8ZMNO2IuQMGw&amp;oe=6AAA1077</t>
+        </is>
+      </c>
+      <c r="O5" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P5" s="178" t="n"/>
       <c r="Q5" s="178" t="n"/>
       <c r="R5" s="178" t="n"/>
       <c r="S5" s="179" t="inlineStr">
         <is>
-          <t>네이버 플레이스 미매칭 / 기각: jejuolletrail:unrelated (Jeju Olle hiking trail account), skipped without fetch</t>
+          <t>상호·주소(논현동 73-39) 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -1977,10 +1989,14 @@
       </c>
       <c r="L14" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M14" s="178" t="n"/>
+          <t>@cific777</t>
+        </is>
+      </c>
+      <c r="M14" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cific777/</t>
+        </is>
+      </c>
       <c r="N14" s="178" t="n"/>
       <c r="O14" s="178" t="n"/>
       <c r="P14" s="178" t="n"/>
@@ -1988,7 +2004,7 @@
       <c r="R14" s="178" t="n"/>
       <c r="S14" s="179" t="inlineStr">
         <is>
-          <t>네이버 플레이스 미매칭 / 기각: pacific_hongdae_live:Pacific HipHop Club (club/bar, DM for table reserve), not a card shop, eastpacifictrade:sneaker bra</t>
+          <t>디스플레이명이 상호+지역+TCG 정확히 일치, 로그인월로 프로필사진/바이오 수치는 확인불가</t>
         </is>
       </c>
     </row>
@@ -2131,10 +2147,14 @@
       </c>
       <c r="L16" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M16" s="178" t="n"/>
+          <t>@rabbitcompany</t>
+        </is>
+      </c>
+      <c r="M16" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rabbitcompany/</t>
+        </is>
+      </c>
       <c r="N16" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20240527_198/1716798296521X8wXX_JPEG/KakaoTalk_20240527_172342594.jpg</t>
@@ -2154,7 +2174,7 @@
       </c>
       <c r="S16" s="179" t="inlineStr">
         <is>
-          <t>네이버 등록 링크 @rabbits_magazine 은 프로필 대조 결과 무관 계정으로 판단 / 기각: rabbits_magazine:could not verify — LOGIN_WALL (18+) on first try, NOT_FOUND on retries with hl=ko and no-hl</t>
+          <t>상호명 정확 일치하나 매 시도 로그인월로 세부정보 미확인, 최종확신도 중간</t>
         </is>
       </c>
     </row>
@@ -2210,10 +2230,14 @@
       </c>
       <c r="L17" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M17" s="178" t="n"/>
+          <t>@xoxo_xoplay</t>
+        </is>
+      </c>
+      <c r="M17" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/xoxo_xoplay/</t>
+        </is>
+      </c>
       <c r="N17" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20220720_167/16583277440531HgNx_PNG/xoplay_logo.png</t>
@@ -2224,7 +2248,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P17" s="178" t="n"/>
+      <c r="P17" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/778735642_17904243465521557_1800504382826832970_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=du4rUfXz6d4Q7kNvwGdHkA3&amp;_nc_oc=AdpJh8v5-FNwQVFT2WZYelsKBxGR7TC-pti-0okOWzjIUtqaKg7w5N2kY-v8TZvq1eQ&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=jbkidc5UchhtJhCto8Ai5A&amp;_nc_ss=7fa02&amp;oh=00_AQJ1XcUyaCFExJsAabEt1iSpHyWeMeze3DCLcOqnI35FQQ&amp;oe=6AA9F085</t>
+        </is>
+      </c>
       <c r="Q17" s="178" t="inlineStr">
         <is>
           <t>@xoxo_xoplay</t>
@@ -2237,7 +2265,7 @@
       </c>
       <c r="S17" s="179" t="inlineStr">
         <is>
-          <t>기각: xoxo__nine:LOGIN_WALL (18+) on both en/ko attempts, unverifiable, xoplay.kr:display 'XOPLAY', generic 'X to O' fun brand</t>
+          <t>주소 완전 일치 확인</t>
         </is>
       </c>
     </row>
@@ -2546,10 +2574,14 @@
       </c>
       <c r="L21" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M21" s="178" t="n"/>
+          <t>@geartown_kr</t>
+        </is>
+      </c>
+      <c r="M21" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/geartown_kr/</t>
+        </is>
+      </c>
       <c r="N21" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20240403_44/1712122052483HxptB_JPEG/geartownv_Mini.jpg</t>
@@ -2560,7 +2592,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P21" s="178" t="n"/>
+      <c r="P21" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/673064020_17859741531652113_3971998025505593520_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=byNS6kQiA_YQ7kNvwFhX_4B&amp;_nc_oc=Adp6-3cJnZBTISW77beo1hWF1KF3HtTLWjVTh5p3ph7U3cPZ6VlgtN2AUsN9h4gBExc&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=nl1L8gA_NNDtSGjbSL8opA&amp;_nc_ss=7fa02&amp;oh=00_AQIFnBN00cyKNCBCEYPoAA8YRGCD8BgffgK6_Eo3XEsl3w&amp;oe=6AAA18BE</t>
+        </is>
+      </c>
       <c r="Q21" s="178" t="n"/>
       <c r="R21" s="180" t="inlineStr">
         <is>
@@ -2569,7 +2605,7 @@
       </c>
       <c r="S21" s="179" t="inlineStr">
         <is>
-          <t>기각: geartown.nl:'Gear Town' but tactical/military gear dealer based in Netherlands, unrelated to TCG</t>
+          <t>상호명 정확 일치 + TCG전문점 소개</t>
         </is>
       </c>
     </row>
@@ -4359,10 +4395,14 @@
       </c>
       <c r="L44" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M44" s="178" t="n"/>
+          <t>@mtg_osan_tabletop</t>
+        </is>
+      </c>
+      <c r="M44" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mtg_osan_tabletop/</t>
+        </is>
+      </c>
       <c r="N44" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20240802_254/17225562903370Jlxq_JPEG/KakaoTalk_20240801_162835764.jpg</t>
@@ -4373,14 +4413,22 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P44" s="178" t="n"/>
+      <c r="P44" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/588564798_18068686598567060_4446960302598838146_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy41NTMuQzMifQ%3D%3D&amp;_nc_ohc=u7qWjBt3f5YQ7kNvwHFpJFw&amp;_nc_oc=Adou3H1IWJv-1dx5IMmtYCYyAD_AEjgtEtfhVJMZBrgwwmjbym5OSYKXRISvfJSPtrM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=Qcm5xd4NQBCKfVRIV1zwiQ&amp;_nc_ss=7fa02&amp;oh=00_AQK5mZRFDBTOp1ayizAcBuxWHjxqb-cTmBosKsqgzK0VfQ&amp;oe=6AA9FC12</t>
+        </is>
+      </c>
       <c r="Q44" s="178" t="n"/>
       <c r="R44" s="180" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1727987183/home</t>
         </is>
       </c>
-      <c r="S44" s="179" t="n"/>
+      <c r="S44" s="179" t="inlineStr">
+        <is>
+          <t>상호명과 계정명 완전 일치, MTG 취미 계정</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="98" t="inlineStr">
@@ -4817,10 +4865,14 @@
       </c>
       <c r="L50" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M50" s="178" t="n"/>
+          <t>@suwoncardplanet</t>
+        </is>
+      </c>
+      <c r="M50" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/suwoncardplanet/</t>
+        </is>
+      </c>
       <c r="N50" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20230330_298/1680145529289tJ9IU_PNG/KakaoTalk_20220801_160539602.png</t>
@@ -4831,7 +4883,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P50" s="178" t="n"/>
+      <c r="P50" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/315442935_615142147060230_208356614693345007_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=mwMCPcnukbsQ7kNvwHH0lNn&amp;_nc_oc=AdpaLgxE2tKDtUhrhFGjLQwIqQfRHJrCaiWVFgBAZef4_-tEuz8tyF6dFfdjNKE4WM8&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQLYT-m7dEs08vsaI39_eLBnvVbFkZnrmP1-NOlfLOgELw&amp;oe=6AAA10E2</t>
+        </is>
+      </c>
       <c r="Q50" s="178" t="n"/>
       <c r="R50" s="180" t="inlineStr">
         <is>
@@ -4840,7 +4896,7 @@
       </c>
       <c r="S50" s="179" t="inlineStr">
         <is>
-          <t>기각: developer:unrelated generic account, 이름상 명백히 무관하여 미조회</t>
+          <t>주소 완전 일치 확인</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5904,24 @@
       </c>
       <c r="L63" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M63" s="178" t="n"/>
-      <c r="N63" s="178" t="n"/>
-      <c r="O63" s="178" t="n"/>
+          <t>@hero_incheon</t>
+        </is>
+      </c>
+      <c r="M63" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hero_incheon/</t>
+        </is>
+      </c>
+      <c r="N63" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/154288014_1171115076682637_9007876840583406219_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=wAXo6AK8b98Q7kNvwFruWoL&amp;_nc_oc=Ado0ssMs5d7ZO5aZMhwk5RL6Yb8dh1N_oCybyg10uUGqq0V5HkJv5j0iItsZhwSwk9U&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQKIJOLouVDRW3_51LaRpA-MQ0ujWELL_QdSLSXZonyvUg&amp;oe=6AAA165E</t>
+        </is>
+      </c>
+      <c r="O63" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P63" s="178" t="n"/>
       <c r="Q63" s="178" t="n"/>
       <c r="R63" s="180" t="inlineStr">
@@ -5863,7 +5931,7 @@
       </c>
       <c r="S63" s="179" t="inlineStr">
         <is>
-          <t>기각: withbupyeong:district government account (부평구청), not the shop</t>
+          <t>상호(히어로즈)+부평구 지역 일치 보드게임카페, 정확 도로명주소만 시트와 다름(시장로 vs 대정로, 동일구 인근 가능성)</t>
         </is>
       </c>
     </row>
@@ -5923,10 +5991,14 @@
       </c>
       <c r="L64" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M64" s="178" t="n"/>
+          <t>@card_pop_tcg</t>
+        </is>
+      </c>
+      <c r="M64" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/card_pop_tcg/</t>
+        </is>
+      </c>
       <c r="N64" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20230324_276/1679637980888PyG43_PNG/01_MAIN_LOGO.png</t>
@@ -5937,7 +6009,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P64" s="178" t="n"/>
+      <c r="P64" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309069098_800997834571738_650317083911657848_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4yNDQuQzMifQ%3D%3D&amp;_nc_ohc=Zv4vqidachoQ7kNvwG1Ps25&amp;_nc_oc=AdpLvTxPR7mX9y8mns-XzA4AqnYsTT2RYKK4mQYm_VohSrxMQeGjL5S3ejdACaOCYYo&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQIOwSHXQRmrVzl46eo2N3SQJ4IkhO_NGCwefKOpHzlqzA&amp;oe=6AA9FC37</t>
+        </is>
+      </c>
       <c r="Q64" s="178" t="n"/>
       <c r="R64" s="180" t="inlineStr">
         <is>
@@ -5946,7 +6022,7 @@
       </c>
       <c r="S64" s="179" t="inlineStr">
         <is>
-          <t>기각: bagelist_seoul:unrelated (bagel bakery brand)</t>
+          <t>계정명(Card_POP)·핸들 내 tcg 표기로 상호와 정확 일치, 바이오는 노출되지 않아 주소 재확인 불가</t>
         </is>
       </c>
     </row>
@@ -6547,18 +6623,30 @@
       </c>
       <c r="L72" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M72" s="178" t="n"/>
-      <c r="N72" s="178" t="n"/>
-      <c r="O72" s="178" t="n"/>
+          <t>@cardprime_cheonan</t>
+        </is>
+      </c>
+      <c r="M72" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cardprime_cheonan/</t>
+        </is>
+      </c>
+      <c r="N72" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/753652075_18073283945413101_8733155674006592954_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy41ODIuQzMifQ%3D%3D&amp;_nc_ohc=Hcc2O8LtlVkQ7kNvwGGdQqg&amp;_nc_oc=AdpexZvqlyVCYxmc6Ko0WpwOuhAUiawFV7UclyIXQd_sr52QyOfvhpuNj_6sf0FBijM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=8YBmi33O8WkYR3bnkujv2g&amp;_nc_ss=7fa02&amp;oh=00_AQL-63gVZ4ZnauBBREaRa7-nQwSpGngq6O3UvxWsmdCcfg&amp;oe=6AAA1211</t>
+        </is>
+      </c>
+      <c r="O72" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P72" s="178" t="n"/>
       <c r="Q72" s="178" t="n"/>
       <c r="R72" s="178" t="n"/>
       <c r="S72" s="179" t="inlineStr">
         <is>
-          <t>네이버 플레이스 미매칭 / 기각: sosostore_cheonan:unrelated (gacha/trinket shop, different brand), mollangmollang_:NOT_FOUND</t>
+          <t>주소·상호 완전 일치, 확실</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6702,24 @@
       </c>
       <c r="L73" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M73" s="178" t="n"/>
-      <c r="N73" s="178" t="n"/>
-      <c r="O73" s="178" t="n"/>
+          <t>@tcg.korea</t>
+        </is>
+      </c>
+      <c r="M73" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tcg.korea/</t>
+        </is>
+      </c>
+      <c r="N73" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/475213441_963916098589214_339027353845888482_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=_H6APxHHzA8Q7kNvwFGVkuh&amp;_nc_oc=AdoGnbC4xodvM9C4SLvriO67V3UEsjIn28AO4rNGbIfsH1YcTWfsmLcH5NmZVmjnzD8&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQIiwFzTUihSutUaHHo3iDlpCBZqx1xw-rhT3wdhh9-eLQ&amp;oe=6AA9EB84</t>
+        </is>
+      </c>
+      <c r="O73" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P73" s="178" t="n"/>
       <c r="Q73" s="178" t="n"/>
       <c r="R73" s="180" t="inlineStr">
@@ -6629,7 +6729,7 @@
       </c>
       <c r="S73" s="179" t="inlineStr">
         <is>
-          <t>기각: asmodee_korea:different entity (board game publisher/distributor, not this shop)</t>
+          <t>상호명은 정확히 일치하나 대전 주소 확인은 안됨(바이오에 주소 없음), 팔로워 8명으로 소규모라 신뢰도 중간</t>
         </is>
       </c>
     </row>
@@ -7060,18 +7160,30 @@
       </c>
       <c r="L79" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M79" s="178" t="n"/>
-      <c r="N79" s="178" t="n"/>
-      <c r="O79" s="178" t="n"/>
+          <t>@tcgfactory.mokpo</t>
+        </is>
+      </c>
+      <c r="M79" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tcgfactory.mokpo/</t>
+        </is>
+      </c>
+      <c r="N79" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/610694292_17844270276668664_2486344436821599950_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy41NTguQzMifQ%3D%3D&amp;_nc_ohc=nCqEZJQ5-PoQ7kNvwEbohgr&amp;_nc_oc=Adp0PYwc9b5wVH5SEZagtbs_EQXjbz8HZzMlJlQyqMGIMtpoLqpoOGfZ80QrWGBx-n4&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=Em3s0KEkFdh-lUd1wOKxWA&amp;_nc_ss=7fa02&amp;oh=00_AQItvMc4nOeRa71ghJgrfEaIyqNKr0FvRbKah0EzlY0KCg&amp;oe=6AA9F5B3</t>
+        </is>
+      </c>
+      <c r="O79" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P79" s="178" t="n"/>
       <c r="Q79" s="178" t="n"/>
       <c r="R79" s="178" t="n"/>
       <c r="S79" s="179" t="inlineStr">
         <is>
-          <t>네이버 플레이스 미매칭 / 기각: eyefactory_mokpo:NOT_FOUND (hl=en and hl=ko both inconclusive)</t>
+          <t>상호명 정확 일치</t>
         </is>
       </c>
     </row>
@@ -7522,10 +7634,14 @@
       </c>
       <c r="L85" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M85" s="178" t="n"/>
+          <t>@trainerschool</t>
+        </is>
+      </c>
+      <c r="M85" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trainerschool/</t>
+        </is>
+      </c>
       <c r="N85" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20230329_52/1680082929583k5VB0_JPEG/IMG_20230111_120640_120.jpg</t>
@@ -7536,7 +7652,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P85" s="178" t="n"/>
+      <c r="P85" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/325197695_1303313530248452_8871863789794651571_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=WTDEI5euFIYQ7kNvwHxxjxy&amp;_nc_oc=Adq1NL7aPeFSpr-YERU2E8YnBUb4WhvyGNUwdrb_lssOK84UG2nrNljgR3npVkVPiqA&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJdq2BVs6GLWeax97dvVw549qnvqu0HBiYJU2QwiX8L6A&amp;oe=6AA9F8C0</t>
+        </is>
+      </c>
       <c r="Q85" s="178" t="n"/>
       <c r="R85" s="180" t="inlineStr">
         <is>
@@ -7545,7 +7665,7 @@
       </c>
       <c r="S85" s="179" t="inlineStr">
         <is>
-          <t>기각: mindschool7:이름상 무관(마인드스쿨) 추정, 미조회</t>
+          <t>상호+지역 일치</t>
         </is>
       </c>
     </row>
@@ -7759,10 +7879,14 @@
       </c>
       <c r="L88" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M88" s="178" t="n"/>
+          <t>@ulsan_tcgfactory</t>
+        </is>
+      </c>
+      <c r="M88" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ulsan_tcgfactory/</t>
+        </is>
+      </c>
       <c r="N88" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20240505_259/1714920367997Mfu5F_JPEG/23DE49A2-9E4B-4142-9CC4-0267B54AA673.jpeg</t>
@@ -7773,7 +7897,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P88" s="178" t="n"/>
+      <c r="P88" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/379327449_1374713926756093_1259750207633737077_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=SmA3XqHC9NMQ7kNvwGfHDqw&amp;_nc_oc=Adr3Otg1Q51EL4C9GOH6EkpeF1AqxVf_GLSYpxnFRL4Qp8Zk802kfVgsrqZXOwE4EB8&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJXaR9d2mdfmhW98wFZ4TqtTEzpQFHhGqeT25oZ06sy7A&amp;oe=6AA9F831</t>
+        </is>
+      </c>
       <c r="Q88" s="178" t="n"/>
       <c r="R88" s="180" t="inlineStr">
         <is>
@@ -7782,7 +7910,7 @@
       </c>
       <c r="S88" s="179" t="inlineStr">
         <is>
-          <t>기각: barbecuefactory_ulsan:이름상 무관(바베큐) 추정, 미조회, sonaki.factory:소나기 팩토리(청소업체), 이름/업종 불일치</t>
+          <t>주소(번영로 454-1) 완전 일치</t>
         </is>
       </c>
     </row>
@@ -7838,10 +7966,14 @@
       </c>
       <c r="L89" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M89" s="178" t="n"/>
+          <t>@tcg_dual.factory</t>
+        </is>
+      </c>
+      <c r="M89" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tcg_dual.factory/</t>
+        </is>
+      </c>
       <c r="N89" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20241217_65/1734426138021QCJ6j_JPEG/KakaoTalk_20241018_192853533_%BA%B9%BB%E7.jpg</t>
@@ -7852,7 +7984,11 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P89" s="178" t="n"/>
+      <c r="P89" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.75761-19/491510825_17843044539473933_3379864865474468053_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=hmkGm02dKBwQ7kNvwEn2UPw&amp;_nc_oc=AdoeE-UN8jIWv1hnSLMZwgHtiWxAT_BCfyqtRSZ7Jj5hzvHwuSFO7mouPayIEdhOJrg&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=ECV2jwjDS9XweLjza7Muog&amp;_nc_ss=7fa02&amp;oh=00_AQIeyLNWPVaP8OpbZJQNSmpQaZuypT38RkWwztvh8X0MrA&amp;oe=6AAA16C7</t>
+        </is>
+      </c>
       <c r="Q89" s="178" t="n"/>
       <c r="R89" s="180" t="inlineStr">
         <is>
@@ -7861,7 +7997,7 @@
       </c>
       <c r="S89" s="179" t="inlineStr">
         <is>
-          <t>기각: jigu_carpenter:이름상 무관(목공) 추정, 미조회, ulsan_carspace:이름상 무관(자동차) 추정, 미조회</t>
+          <t>상호명 완전 일치(바이오 주소는 454-1로 표기돼 등록주소 36-8과 다르나 계정명 자체가 확정적)</t>
         </is>
       </c>
     </row>
@@ -8051,18 +8187,30 @@
       </c>
       <c r="L92" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M92" s="178" t="n"/>
-      <c r="N92" s="178" t="n"/>
-      <c r="O92" s="178" t="n"/>
+          <t>@boardgame_cafe_miniville</t>
+        </is>
+      </c>
+      <c r="M92" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boardgame_cafe_miniville/</t>
+        </is>
+      </c>
+      <c r="N92" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/60326143_2047940975501969_1143401241443827712_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=DqfVktWhcYEQ7kNvwFjXYTg&amp;_nc_oc=AdotdecOIE7tS01P0OmK7MGHdofMQjKlbIzDZyhoX-1JjnKXsT4T6yMydIoZWwXbOWk&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQLOMhAA8cWdiahR3G-vqqbZspW08AA5h7lpt1n5NQOt2g&amp;oe=6AA9EA2B</t>
+        </is>
+      </c>
+      <c r="O92" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P92" s="178" t="n"/>
       <c r="Q92" s="178" t="n"/>
       <c r="R92" s="178" t="n"/>
       <c r="S92" s="179" t="inlineStr">
         <is>
-          <t>네이버 플레이스 미매칭 / 기각: com2us_minigame:이름상 무관(컴투스 게임사) 추정, 미조회, hero_stagram_:이름상 무관 추정, 미조회, tamsk_boardgame:NOT_FOUND(hl=en, hl=ko 재시도)</t>
+          <t>상호+서면(부산진구) 지역 일치</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8669,24 @@
       </c>
       <c r="L98" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M98" s="178" t="n"/>
-      <c r="N98" s="178" t="n"/>
-      <c r="O98" s="178" t="n"/>
+          <t>@busantherak</t>
+        </is>
+      </c>
+      <c r="M98" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/busantherak/</t>
+        </is>
+      </c>
+      <c r="N98" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/631002986_17843380524687041_3579115282959286250_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=akbSTyYJKA4Q7kNvwHnlwAi&amp;_nc_oc=AdpjWU7htQ9k-n9f6vsfEZ5-w-IIDdjV-TajryYs1O3zzl3I-GYwDzTxlDprhJRjzk4&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=J7RTVEfOuB7PGg7RQSTUVA&amp;_nc_ss=7fa02&amp;oh=00_AQJKGFz9j1PFhY61RUOE-Yy3fH7Jt8k0nLRUGJjL2UGfIg&amp;oe=6AAA0479</t>
+        </is>
+      </c>
+      <c r="O98" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P98" s="178" t="n"/>
       <c r="Q98" s="178" t="n"/>
       <c r="R98" s="180" t="inlineStr">
@@ -8536,7 +8696,7 @@
       </c>
       <c r="S98" s="179" t="inlineStr">
         <is>
-          <t>기각: musicoftheNightKr:이름상 무관 추정, 미조회, drinking_boys_and_girls_choir:이름상 무관 추정, 미조회, se_so_neon:이름상 무관(음악밴드) 추정, 미조회, cant_be</t>
+          <t>상호+주소(수영동 444-15) 완전 일치</t>
         </is>
       </c>
     </row>
@@ -8592,10 +8752,14 @@
       </c>
       <c r="L99" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M99" s="178" t="n"/>
+          <t>@korkr1</t>
+        </is>
+      </c>
+      <c r="M99" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/korkr1/</t>
+        </is>
+      </c>
       <c r="N99" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20260131_103/1769863247972E3pi6_JPEG/1000023533.jpg</t>
@@ -8606,14 +8770,22 @@
           <t>네이버 플레이스</t>
         </is>
       </c>
-      <c r="P99" s="178" t="n"/>
+      <c r="P99" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/438454074_266863139849224_7190106814264244219_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=upp2Tvg2l6wQ7kNvwFBrk2O&amp;_nc_oc=AdoPo8O3D_tQYG7uI37EP5t3DnKq54twLUeJADbYaG0HXu2qloEe16JIDhSFOkpF13Q&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQKto72lEmxNCVnvC7O0poZ-Kk7mXQV6ZUsIlD32Tfh4yQ&amp;oe=6AAA0816</t>
+        </is>
+      </c>
       <c r="Q99" s="178" t="n"/>
       <c r="R99" s="180" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1451790555/home</t>
         </is>
       </c>
-      <c r="S99" s="179" t="n"/>
+      <c r="S99" s="179" t="inlineStr">
+        <is>
+          <t>원 후보(tcggymcafe)가 새 계정 korkr1로 이전 안내함, 창원 지역 일치로 korkr1 채택</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="102" t="inlineStr">
@@ -8817,12 +8989,24 @@
       </c>
       <c r="L102" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M102" s="178" t="n"/>
-      <c r="N102" s="178" t="n"/>
-      <c r="O102" s="178" t="n"/>
+          <t>@cardelixir_01</t>
+        </is>
+      </c>
+      <c r="M102" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cardelixir_01/</t>
+        </is>
+      </c>
+      <c r="N102" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/760192577_18057644129566231_4204041799292419440_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy45MjIuQzMifQ%3D%3D&amp;_nc_ohc=I-mwv22ZoPIQ7kNvwFHW89r&amp;_nc_oc=AdpUQRpfj3QidyRrOLLc41500bWmBiPPJT4HdTFtRw1nHWb8PIV0B5nDXKo7xw07anU&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=QH5bqr_iNdgLnPNEEJNXvg&amp;_nc_ss=7fa02&amp;oh=00_AQJ7FhNHzcm1ah0OctfKySfassLhLJSBqfRJ6HwxjOg7fw&amp;oe=6AAA0691</t>
+        </is>
+      </c>
+      <c r="O102" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="P102" s="178" t="n"/>
       <c r="Q102" s="178" t="n"/>
       <c r="R102" s="180" t="inlineStr">
@@ -8830,7 +9014,11 @@
           <t>https://m.place.naver.com/place/2097527194/home</t>
         </is>
       </c>
-      <c r="S102" s="179" t="n"/>
+      <c r="S102" s="179" t="inlineStr">
+        <is>
+          <t>상호+주소(합성남7길 31, 3층) 완전 일치</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="48" customHeight="1">
       <c r="A103" s="102" t="inlineStr">
@@ -9117,10 +9305,14 @@
       </c>
       <c r="L106" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="M106" s="178" t="n"/>
+          <t>@iboxjeju</t>
+        </is>
+      </c>
+      <c r="M106" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iboxjeju/</t>
+        </is>
+      </c>
       <c r="N106" s="180" t="inlineStr">
         <is>
           <t>https://ldb-phinf.pstatic.net/20240503_45/1714719207866Ym0xI_JPEG/1704318930104-1.jpg</t>
@@ -9140,7 +9332,7 @@
       </c>
       <c r="S106" s="179" t="inlineStr">
         <is>
-          <t>네이버 등록 링크 @islandb_cafe 은 프로필 대조 결과 무관 계정으로 판단 / 기각: islandb_cafe:아일랜드비(와플/디저트 카페), 업종 불일치</t>
+          <t>상호('아일랜드')+지역(제주) 일치로 채택, 다만 바이오/팔로워 등 상세 데이터는 페이지에서 확인 못함(제목만 확인)</t>
         </is>
       </c>
     </row>
@@ -9150,212 +9342,249 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R87" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R88" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R89" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R91" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R93" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R94" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R95" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R96" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N97" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R97" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R98" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N99" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R99" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R100" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R101" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R102" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N103" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R103" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N104" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R104" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R105" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R106" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R75" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R76" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R87" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R88" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R89" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R91" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R93" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R94" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R95" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R96" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N97" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R97" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N98" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R98" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N99" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R99" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R100" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R101" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R102" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N103" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R103" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N104" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R104" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R105" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R106" r:id="rId239"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId203"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId240"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9601,18 +9830,30 @@
       </c>
       <c r="N5" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O5" s="178" t="n"/>
-      <c r="P5" s="178" t="n"/>
-      <c r="Q5" s="178" t="n"/>
+          <t>@beems.cardshop</t>
+        </is>
+      </c>
+      <c r="O5" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beems.cardshop/</t>
+        </is>
+      </c>
+      <c r="P5" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/187567881_183020520254090_1916987080649099423_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTAuQzMifQ%3D%3D&amp;_nc_ohc=wzZnLPtiIrEQ7kNvwEDCZrp&amp;_nc_oc=Adqn6WhrjC2f2AjaE1o-I3x0aiWxGULVMu1VwVFPPKz-qMGNF4vMOfCbk73OSwidOFg&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJLkbraABgW8akEdoIcZ_zm81gfs9DITzvZE07jm_0zSw&amp;oe=6AA9F922</t>
+        </is>
+      </c>
+      <c r="Q5" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R5" s="178" t="n"/>
       <c r="S5" s="178" t="n"/>
       <c r="T5" s="178" t="n"/>
       <c r="U5" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명·소개가 매장명과 정확히 일치 (아키하바라 트레카샵)</t>
         </is>
       </c>
     </row>
@@ -9676,18 +9917,30 @@
       </c>
       <c r="N6" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O6" s="178" t="n"/>
-      <c r="P6" s="178" t="n"/>
-      <c r="Q6" s="178" t="n"/>
+          <t>@hobby_anko_akihabara</t>
+        </is>
+      </c>
+      <c r="O6" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hobby_anko_akihabara/</t>
+        </is>
+      </c>
+      <c r="P6" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/590410865_17845789029611863_2157111525072617029_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4zMjAuQzMifQ%3D%3D&amp;_nc_ohc=hL7gppmOGDQQ7kNvwHeqczq&amp;_nc_oc=AdrA-lsiFNYN8iSONsuZ-LbydS4MfXWt6P-9ti49aFLlV8q6FyBTXBWR2KmBq7pO9rw&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=D53k9uzLh1PkS5sRau4QQw&amp;_nc_ss=7fa02&amp;oh=00_AQLd137CFI0LLVLi24CViXQfVKEtfT2BM81F3YRt-FA9rg&amp;oe=6AA9E4F7</t>
+        </is>
+      </c>
+      <c r="Q6" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R6" s="178" t="n"/>
       <c r="S6" s="178" t="n"/>
       <c r="T6" s="178" t="n"/>
       <c r="U6" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명이 매장명(ANKOU, Akihabara)과 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -9755,18 +10008,30 @@
       </c>
       <c r="N7" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O7" s="178" t="n"/>
-      <c r="P7" s="178" t="n"/>
-      <c r="Q7" s="178" t="n"/>
+          <t>@toreca_pocketcenter_akihabara</t>
+        </is>
+      </c>
+      <c r="O7" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/toreca_pocketcenter_akihabara/</t>
+        </is>
+      </c>
+      <c r="P7" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.75761-19/497982445_17945533796991260_4372598551508402763_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=A3cAmIuGgCUQ7kNvwFfwyKP&amp;_nc_oc=AdokM3BjFrU_InpthjZ4dW-DVny-3oVSwDy4H3tP6cRrf0OyNXmHxrKbv6ReodSz0N0&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=d0hwjqgLojnN690m2nc1LQ&amp;_nc_ss=7fa02&amp;oh=00_AQKAOY_UA6BNnO_TZ-mrpTZaQ1WZSqiBWKOgQ_BUTrtlOg&amp;oe=6AA9F56B</t>
+        </is>
+      </c>
+      <c r="Q7" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R7" s="178" t="n"/>
       <c r="S7" s="178" t="n"/>
       <c r="T7" s="178" t="n"/>
       <c r="U7" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명이 매장명(Pocket Center Akihabara)과 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -9830,18 +10095,30 @@
       </c>
       <c r="N8" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O8" s="178" t="n"/>
-      <c r="P8" s="178" t="n"/>
-      <c r="Q8" s="178" t="n"/>
+          <t>@tradingcardshop_yk</t>
+        </is>
+      </c>
+      <c r="O8" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tradingcardshop_yk/</t>
+        </is>
+      </c>
+      <c r="P8" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/486021112_1237214744569648_3337745128284898241_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDgwLkMzIn0%3D&amp;_nc_ohc=m5wwTE-6fgEQ7kNvwFQS6Q2&amp;_nc_oc=AdqY-gXEAc3M4gatNEHm-8HdhiGOD5wiAaFl_TWhM8qAz-AtC5cHiVmRdqiuWLHPo7Q&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQLJmjpJYdZPjpp2_UBlt7M1it6xc1SRpM8bLtP5U8ib1w&amp;oe=6AAA0BAF</t>
+        </is>
+      </c>
+      <c r="Q8" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R8" s="178" t="n"/>
       <c r="S8" s="178" t="n"/>
       <c r="T8" s="178" t="n"/>
       <c r="U8" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명이 매장명(Trading Card Shop YK)과 정확히 일치, 아키하바라 소개</t>
         </is>
       </c>
     </row>
@@ -10056,12 +10333,24 @@
       </c>
       <c r="N11" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O11" s="178" t="n"/>
-      <c r="P11" s="178" t="n"/>
-      <c r="Q11" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O11" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P11" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q11" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R11" s="178" t="n"/>
       <c r="S11" s="178" t="inlineStr">
         <is>
@@ -10069,7 +10358,11 @@
         </is>
       </c>
       <c r="T11" s="178" t="n"/>
-      <c r="U11" s="179" t="n"/>
+      <c r="U11" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정 (지점 개별 계정 아님)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="94" t="inlineStr">
@@ -10134,12 +10427,24 @@
       </c>
       <c r="N12" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O12" s="178" t="n"/>
-      <c r="P12" s="178" t="n"/>
-      <c r="Q12" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O12" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P12" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q12" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R12" s="178" t="n"/>
       <c r="S12" s="178" t="inlineStr">
         <is>
@@ -10147,7 +10452,11 @@
         </is>
       </c>
       <c r="T12" s="178" t="n"/>
-      <c r="U12" s="179" t="n"/>
+      <c r="U12" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정 (row11과 동일 계정)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="94" t="inlineStr">
@@ -10212,10 +10521,14 @@
       </c>
       <c r="N13" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O13" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O13" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P13" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_menu/img_2604_hare2anex.webp</t>
@@ -10226,14 +10539,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R13" s="178" t="n"/>
+      <c r="R13" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S13" s="178" t="inlineStr">
         <is>
           <t>@hareruya2pokeca</t>
         </is>
       </c>
       <c r="T13" s="178" t="n"/>
-      <c r="U13" s="179" t="n"/>
+      <c r="U13" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 공식 브랜드 계정, 아키하바라 매장 언급</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="94" t="inlineStr">
@@ -10298,10 +10619,14 @@
       </c>
       <c r="N14" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O14" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O14" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P14" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_tower/img_2601_towerA.webp</t>
@@ -10312,14 +10637,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R14" s="178" t="n"/>
+      <c r="R14" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S14" s="178" t="inlineStr">
         <is>
           <t>@hareruya2tower</t>
         </is>
       </c>
       <c r="T14" s="178" t="n"/>
-      <c r="U14" s="179" t="n"/>
+      <c r="U14" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 공식 브랜드 계정 (row13과 동일 계정)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="94" t="inlineStr">
@@ -10464,18 +10797,30 @@
       </c>
       <c r="N16" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O16" s="178" t="n"/>
-      <c r="P16" s="178" t="n"/>
-      <c r="Q16" s="178" t="n"/>
+          <t>@ninnin_ikebukuro</t>
+        </is>
+      </c>
+      <c r="O16" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ninnin_ikebukuro/</t>
+        </is>
+      </c>
+      <c r="P16" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/474641042_1860580054770138_624441163166973666_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4zOTguQzMifQ%3D%3D&amp;_nc_ohc=POvE1aTUJiUQ7kNvwGbWM70&amp;_nc_oc=Ado13JfSzxGRuyppOFXt69Ecd5Cg5OyCDyil8SyN5B8uMYjhOzNfxqtrugcXPtwRWgY&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQLZbvE_UD-XtvPeKILos6MMjz4et0Q89-_TZVpRlChIwg&amp;oe=6AA9F713</t>
+        </is>
+      </c>
+      <c r="Q16" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R16" s="178" t="n"/>
       <c r="S16" s="178" t="n"/>
       <c r="T16" s="178" t="n"/>
       <c r="U16" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명이 매장명(Ninnin Ikebukuro)과 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -10612,18 +10957,30 @@
       </c>
       <c r="N18" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O18" s="178" t="n"/>
-      <c r="P18" s="178" t="n"/>
-      <c r="Q18" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O18" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P18" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q18" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R18" s="178" t="n"/>
       <c r="S18" s="178" t="n"/>
       <c r="T18" s="178" t="n"/>
       <c r="U18" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정</t>
         </is>
       </c>
     </row>
@@ -10690,10 +11047,14 @@
       </c>
       <c r="N19" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O19" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O19" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P19" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_ikebukuro/ikebukuro.webp</t>
@@ -10704,14 +11065,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R19" s="178" t="n"/>
+      <c r="R19" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S19" s="178" t="inlineStr">
         <is>
           <t>@hareruya2ikbkr</t>
         </is>
       </c>
       <c r="T19" s="178" t="n"/>
-      <c r="U19" s="179" t="n"/>
+      <c r="U19" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 공식 브랜드 계정</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="94" t="inlineStr">
@@ -10946,18 +11315,30 @@
       </c>
       <c r="N22" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O22" s="178" t="n"/>
-      <c r="P22" s="178" t="n"/>
-      <c r="Q22" s="178" t="n"/>
+          <t>@onepiece_base_shop</t>
+        </is>
+      </c>
+      <c r="O22" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onepiece_base_shop/</t>
+        </is>
+      </c>
+      <c r="P22" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/541677351_17846369196559241_2506064694596702095_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=jBLhL6dyVAEQ7kNvwEmGYMX&amp;_nc_oc=AdqsYSs6X4jNaNDy76TN5g9I_L_3lsIZwXQKyKdaFkgMLCwDqlVeHyB6RLNlJITkRHY&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=khcbTIRWzv_RqZYAsl2eIQ&amp;_nc_ss=7fa02&amp;oh=00_AQJjr8fI8XcZ9owjL7Os2uuCbYrNBcCeI4rpdRyagqKMgg&amp;oe=6AA9EDFD</t>
+        </is>
+      </c>
+      <c r="Q22" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R22" s="178" t="n"/>
       <c r="S22" s="178" t="n"/>
       <c r="T22" s="178" t="n"/>
       <c r="U22" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>공식 인증(verified) 계정, 신주쿠 마루이 본관 4F 주소 일치</t>
         </is>
       </c>
     </row>
@@ -11024,10 +11405,14 @@
       </c>
       <c r="N23" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O23" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O23" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P23" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_menu/img_2606_babaTOP.webp</t>
@@ -11038,14 +11423,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R23" s="178" t="n"/>
+      <c r="R23" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S23" s="178" t="inlineStr">
         <is>
           <t>@hareruya2pokeca</t>
         </is>
       </c>
       <c r="T23" s="178" t="n"/>
-      <c r="U23" s="179" t="n"/>
+      <c r="U23" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 공식 브랜드 계정</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="94" t="inlineStr">
@@ -11111,18 +11504,30 @@
       </c>
       <c r="N24" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O24" s="178" t="n"/>
-      <c r="P24" s="178" t="n"/>
-      <c r="Q24" s="178" t="n"/>
+          <t>@batonstorenakanobw</t>
+        </is>
+      </c>
+      <c r="O24" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/batonstorenakanobw/</t>
+        </is>
+      </c>
+      <c r="P24" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/365457357_3454375531452775_4647388297390732732_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4zMjAuQzMifQ%3D%3D&amp;_nc_ohc=6be2W7EYbkYQ7kNvwG45uiS&amp;_nc_oc=AdqKYx8tBDoAAk1yg8x_4aY6WagSLRjtb_GIQyQ0uPKQhwjmsKwca5uql-HzfA_r6Bw&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJNUxaY0q7SvAA-h_ORdUbLQRUy9u28WD9EtdYcyQ6pvA&amp;oe=6AAA1B59</t>
+        </is>
+      </c>
+      <c r="Q24" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R24" s="178" t="n"/>
       <c r="S24" s="178" t="n"/>
       <c r="T24" s="178" t="n"/>
       <c r="U24" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>표시명이 매장명과 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -11269,18 +11674,30 @@
       </c>
       <c r="N26" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O26" s="178" t="n"/>
-      <c r="P26" s="178" t="n"/>
-      <c r="Q26" s="178" t="n"/>
+          <t>@amtaf0306</t>
+        </is>
+      </c>
+      <c r="O26" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amtaf0306/</t>
+        </is>
+      </c>
+      <c r="P26" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/460926357_887618919945947_9062114617442013563_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=3pNWGwGGLMIQ7kNvwFRd3fM&amp;_nc_oc=Ado5zfFbYU0ms4azDJ2EDmRHvMLPuoT3epvPv0qmbkXeZw4xO9I54EHzLEG9RwXIRv4&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJNSbPA5JMwDcRS9VpEGzeM7duO68yx1fT5S6BV6xYhSg&amp;oe=6AA9EF06</t>
+        </is>
+      </c>
+      <c r="Q26" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R26" s="178" t="n"/>
       <c r="S26" s="178" t="n"/>
       <c r="T26" s="178" t="n"/>
       <c r="U26" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>주소(日本橋4-15-1)까지 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -11429,18 +11846,30 @@
       </c>
       <c r="N28" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O28" s="178" t="n"/>
-      <c r="P28" s="178" t="n"/>
-      <c r="Q28" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O28" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P28" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q28" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R28" s="178" t="n"/>
       <c r="S28" s="178" t="n"/>
       <c r="T28" s="178" t="n"/>
       <c r="U28" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정</t>
         </is>
       </c>
     </row>
@@ -11507,18 +11936,30 @@
       </c>
       <c r="N29" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O29" s="178" t="n"/>
-      <c r="P29" s="178" t="n"/>
-      <c r="Q29" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O29" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P29" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q29" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R29" s="178" t="n"/>
       <c r="S29" s="178" t="n"/>
       <c r="T29" s="178" t="n"/>
       <c r="U29" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정</t>
         </is>
       </c>
     </row>
@@ -11581,18 +12022,30 @@
       </c>
       <c r="N30" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O30" s="178" t="n"/>
-      <c r="P30" s="178" t="n"/>
-      <c r="Q30" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O30" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P30" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q30" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R30" s="178" t="n"/>
       <c r="S30" s="178" t="n"/>
       <c r="T30" s="178" t="n"/>
       <c r="U30" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 공식 브랜드 계정</t>
         </is>
       </c>
     </row>
@@ -11659,18 +12112,30 @@
       </c>
       <c r="N31" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O31" s="178" t="n"/>
-      <c r="P31" s="178" t="n"/>
-      <c r="Q31" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O31" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P31" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q31" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R31" s="178" t="n"/>
       <c r="S31" s="178" t="n"/>
       <c r="T31" s="178" t="n"/>
       <c r="U31" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 브랜드 공식 계정(전 지점 공용)</t>
         </is>
       </c>
     </row>
@@ -11737,10 +12202,14 @@
       </c>
       <c r="N32" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O32" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O32" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P32" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.amazonaws.com/page/store_namba/img_2408_Hare2Nanba.webp</t>
@@ -11751,14 +12220,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R32" s="178" t="n"/>
+      <c r="R32" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S32" s="178" t="inlineStr">
         <is>
           <t>@hareruya2namba</t>
         </is>
       </c>
       <c r="T32" s="178" t="n"/>
-      <c r="U32" s="179" t="n"/>
+      <c r="U32" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="128" t="inlineStr">
@@ -11824,18 +12301,30 @@
       </c>
       <c r="N33" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O33" s="178" t="n"/>
-      <c r="P33" s="178" t="n"/>
-      <c r="Q33" s="178" t="n"/>
+          <t>@surugaya_jp</t>
+        </is>
+      </c>
+      <c r="O33" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/surugaya_jp/</t>
+        </is>
+      </c>
+      <c r="P33" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/448634205_3866890380206326_5057204226306541723_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=LPxZKrw5h9gQ7kNvwGqlCQ_&amp;_nc_oc=AdpyS24ALhY4A15EE1GoS8FpmNf8_AoYzyXqHM39jMUiS-qOJfbRrgEfmQJfVRocdUg&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQKyBYI9OIs77hK1GJSmUCd1XtDKL3a69uqCb94PuYt-zA&amp;oe=6AA9E629</t>
+        </is>
+      </c>
+      <c r="Q33" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R33" s="178" t="n"/>
       <c r="S33" s="178" t="n"/>
       <c r="T33" s="178" t="n"/>
       <c r="U33" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 駿河屋 브랜드 공식 계정(전 지점 공용)</t>
         </is>
       </c>
     </row>
@@ -11902,10 +12391,14 @@
       </c>
       <c r="N34" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O34" s="178" t="n"/>
+          <t>@mintcardjapan</t>
+        </is>
+      </c>
+      <c r="O34" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mintcardjapan/</t>
+        </is>
+      </c>
       <c r="P34" s="180" t="inlineStr">
         <is>
           <t>https://img07.shop-pro.jp/PA01031/426/product/4246343.jpg?cmsp_timestamp=20220712151235</t>
@@ -11916,14 +12409,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R34" s="178" t="n"/>
+      <c r="R34" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/604740660_18059372816642657_3350166706630106538_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=7kNCEvzHHZ0Q7kNvwH0X5jm&amp;_nc_oc=AdqnWFt3A1Czngb6c4p3Ci0hbtbJ2W7qHvoJs52tn-b3OjjDI8m7yEK4RaQbJM0NU-E&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=gARWiqER6H87eYbxdJW3WQ&amp;_nc_ss=7fa02&amp;oh=00_AQK7roYcWw-fa3sBdcNy6lUAX9OTzU6PXvQONlnqAB6KwQ&amp;oe=6AAA0A2B</t>
+        </is>
+      </c>
       <c r="S34" s="178" t="inlineStr">
         <is>
           <t>@mint_umeda</t>
         </is>
       </c>
       <c r="T34" s="178" t="n"/>
-      <c r="U34" s="179" t="n"/>
+      <c r="U34" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 MINT 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="132" t="inlineStr">
@@ -11988,10 +12489,14 @@
       </c>
       <c r="N35" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O35" s="178" t="n"/>
+          <t>@mintcardjapan</t>
+        </is>
+      </c>
+      <c r="O35" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mintcardjapan/</t>
+        </is>
+      </c>
       <c r="P35" s="180" t="inlineStr">
         <is>
           <t>https://image.parco.jp/SCCWEB/image/fukuoka/store/storage/w750/shop_cname_20211110115156.jpg</t>
@@ -12002,14 +12507,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R35" s="178" t="n"/>
+      <c r="R35" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/604740660_18059372816642657_3350166706630106538_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=7kNCEvzHHZ0Q7kNvwH0X5jm&amp;_nc_oc=AdqnWFt3A1Czngb6c4p3Ci0hbtbJ2W7qHvoJs52tn-b3OjjDI8m7yEK4RaQbJM0NU-E&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=gARWiqER6H87eYbxdJW3WQ&amp;_nc_ss=7fa02&amp;oh=00_AQK7roYcWw-fa3sBdcNy6lUAX9OTzU6PXvQONlnqAB6KwQ&amp;oe=6AAA0A2B</t>
+        </is>
+      </c>
       <c r="S35" s="178" t="inlineStr">
         <is>
           <t>@mint_fparco</t>
         </is>
       </c>
       <c r="T35" s="178" t="n"/>
-      <c r="U35" s="179" t="n"/>
+      <c r="U35" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 MINT 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="132" t="inlineStr">
@@ -12160,10 +12673,14 @@
       </c>
       <c r="N37" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O37" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O37" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P37" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_fukuoka/250904_hare2fukuoka_toplogo.webp</t>
@@ -12174,14 +12691,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R37" s="178" t="n"/>
+      <c r="R37" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S37" s="178" t="inlineStr">
         <is>
           <t>@hareruya2fkok</t>
         </is>
       </c>
       <c r="T37" s="178" t="n"/>
-      <c r="U37" s="179" t="n"/>
+      <c r="U37" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="132" t="inlineStr">
@@ -12243,18 +12768,30 @@
       </c>
       <c r="N38" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O38" s="178" t="n"/>
-      <c r="P38" s="178" t="n"/>
-      <c r="Q38" s="178" t="n"/>
+          <t>@surugaya_jp</t>
+        </is>
+      </c>
+      <c r="O38" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/surugaya_jp/</t>
+        </is>
+      </c>
+      <c r="P38" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/448634205_3866890380206326_5057204226306541723_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=LPxZKrw5h9gQ7kNvwGqlCQ_&amp;_nc_oc=AdpyS24ALhY4A15EE1GoS8FpmNf8_AoYzyXqHM39jMUiS-qOJfbRrgEfmQJfVRocdUg&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQKyBYI9OIs77hK1GJSmUCd1XtDKL3a69uqCb94PuYt-zA&amp;oe=6AA9E629</t>
+        </is>
+      </c>
+      <c r="Q38" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R38" s="178" t="n"/>
       <c r="S38" s="178" t="n"/>
       <c r="T38" s="178" t="n"/>
       <c r="U38" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 駿河屋 브랜드 공식 계정(전 지점 공용)</t>
         </is>
       </c>
     </row>
@@ -12821,10 +13358,14 @@
       </c>
       <c r="N45" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O45" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O45" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
       <c r="P45" s="180" t="inlineStr">
         <is>
           <t>https://hareruya2-filepool.s3.us-east-1.amazonaws.com/page/store_osu/store_2604_hare2osu.webp</t>
@@ -12835,14 +13376,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R45" s="178" t="n"/>
+      <c r="R45" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
       <c r="S45" s="178" t="inlineStr">
         <is>
           <t>@hareruya2osu</t>
         </is>
       </c>
       <c r="T45" s="178" t="n"/>
-      <c r="U45" s="179" t="n"/>
+      <c r="U45" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="98" t="inlineStr">
@@ -13182,10 +13731,14 @@
       </c>
       <c r="N49" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O49" s="178" t="n"/>
+          <t>@mintcardjapan</t>
+        </is>
+      </c>
+      <c r="O49" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mintcardjapan/</t>
+        </is>
+      </c>
       <c r="P49" s="180" t="inlineStr">
         <is>
           <t>https://img07.shop-pro.jp/PA01031/426/PA01031426.png?cmsp_timestamp=20260909154403</t>
@@ -13196,14 +13749,22 @@
           <t>공식 사이트</t>
         </is>
       </c>
-      <c r="R49" s="178" t="n"/>
+      <c r="R49" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/604740660_18059372816642657_3350166706630106538_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=7kNCEvzHHZ0Q7kNvwH0X5jm&amp;_nc_oc=AdqnWFt3A1Czngb6c4p3Ci0hbtbJ2W7qHvoJs52tn-b3OjjDI8m7yEK4RaQbJM0NU-E&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=gARWiqER6H87eYbxdJW3WQ&amp;_nc_ss=7fa02&amp;oh=00_AQK7roYcWw-fa3sBdcNy6lUAX9OTzU6PXvQONlnqAB6KwQ&amp;oe=6AAA0A2B</t>
+        </is>
+      </c>
       <c r="S49" s="178" t="inlineStr">
         <is>
           <t>@mint_yokohama</t>
         </is>
       </c>
       <c r="T49" s="178" t="n"/>
-      <c r="U49" s="179" t="n"/>
+      <c r="U49" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 MINT 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="136" t="inlineStr">
@@ -13363,18 +13924,30 @@
       </c>
       <c r="N51" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O51" s="178" t="n"/>
-      <c r="P51" s="178" t="n"/>
-      <c r="Q51" s="178" t="n"/>
+          <t>@girafull_kyoto</t>
+        </is>
+      </c>
+      <c r="O51" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/girafull_kyoto/</t>
+        </is>
+      </c>
+      <c r="P51" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/391517219_344074381430524_2106365339851292196_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=XODoE9jMOckQ7kNvwHcMKLM&amp;_nc_oc=AdrBCuFmayALUa1yZRL8H8HSQf3_HxwpMOnEYuVy26f60Xey1V0i4ZhAwfS2EPOJyCw&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJ6Xh07v4pcPzeuMRnnpDpOlHu7VAKMR7QD2VH8bvaVRQ&amp;oe=6AAA08D9</t>
+        </is>
+      </c>
+      <c r="Q51" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R51" s="178" t="n"/>
       <c r="S51" s="178" t="n"/>
       <c r="T51" s="178" t="n"/>
       <c r="U51" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>GIRAFULL 京都店 지점 전용 계정, 상호 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -13601,12 +14174,24 @@
       </c>
       <c r="N54" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O54" s="178" t="n"/>
-      <c r="P54" s="178" t="n"/>
-      <c r="Q54" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O54" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
+      <c r="P54" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
+      <c r="Q54" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R54" s="178" t="n"/>
       <c r="S54" s="178" t="inlineStr">
         <is>
@@ -13614,7 +14199,11 @@
         </is>
       </c>
       <c r="T54" s="178" t="n"/>
-      <c r="U54" s="179" t="n"/>
+      <c r="U54" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 1번 후보(hareruya_kyoto)는 무관 식당이라 거절, 晴れる屋2 브랜드 공식 계정으로 대체</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="52" customHeight="1">
       <c r="A55" s="144" t="inlineStr">
@@ -13680,18 +14269,30 @@
       </c>
       <c r="N55" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O55" s="178" t="n"/>
-      <c r="P55" s="178" t="n"/>
-      <c r="Q55" s="178" t="n"/>
+          <t>@bahamut_7777</t>
+        </is>
+      </c>
+      <c r="O55" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bahamut_7777/</t>
+        </is>
+      </c>
+      <c r="P55" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/482725481_1137710804759509_908970472290347087_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy45NzYuQzMifQ%3D%3D&amp;_nc_ohc=6FVnzn6ceqIQ7kNvwFQruNH&amp;_nc_oc=AdoE_1csyXFz0NmBssASj_cQYKBwDzKDO7yHbzg6wTdGe5u8J1RyPyN0_JwLm_V7waE&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQIm84SgePBjEklVqubIJhgXqaksjT6dIQeeuvjAe-2Anw&amp;oe=6AA9FC3D</t>
+        </is>
+      </c>
+      <c r="Q55" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R55" s="178" t="n"/>
       <c r="S55" s="178" t="n"/>
       <c r="T55" s="178" t="n"/>
       <c r="U55" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>상호 정확히 일치·トレカ샵 명시, 주소는 같은 블록(南2条西5丁目)이나 번지 표기가 13-64/16-34로 약간 다름(빌딩 내 이전/표기차 가능성)</t>
         </is>
       </c>
     </row>
@@ -14014,12 +14615,24 @@
       </c>
       <c r="N59" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O59" s="178" t="n"/>
-      <c r="P59" s="178" t="n"/>
-      <c r="Q59" s="178" t="n"/>
+          <t>@mintcardjapan</t>
+        </is>
+      </c>
+      <c r="O59" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mintcardjapan/</t>
+        </is>
+      </c>
+      <c r="P59" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/604740660_18059372816642657_3350166706630106538_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=7kNCEvzHHZ0Q7kNvwH0X5jm&amp;_nc_oc=AdqnWFt3A1Czngb6c4p3Ci0hbtbJ2W7qHvoJs52tn-b3OjjDI8m7yEK4RaQbJM0NU-E&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=gARWiqER6H87eYbxdJW3WQ&amp;_nc_ss=7fa02&amp;oh=00_AQK7roYcWw-fa3sBdcNy6lUAX9OTzU6PXvQONlnqAB6KwQ&amp;oe=6AAA0A2B</t>
+        </is>
+      </c>
+      <c r="Q59" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R59" s="178" t="n"/>
       <c r="S59" s="178" t="inlineStr">
         <is>
@@ -14027,7 +14640,11 @@
         </is>
       </c>
       <c r="T59" s="178" t="n"/>
-      <c r="U59" s="179" t="n"/>
+      <c r="U59" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 MINT 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="52" customHeight="1">
       <c r="A60" s="148" t="inlineStr">
@@ -14187,12 +14804,24 @@
       </c>
       <c r="N61" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O61" s="178" t="n"/>
-      <c r="P61" s="178" t="n"/>
-      <c r="Q61" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O61" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
+      <c r="P61" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
+      <c r="Q61" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R61" s="178" t="n"/>
       <c r="S61" s="178" t="inlineStr">
         <is>
@@ -14200,7 +14829,11 @@
         </is>
       </c>
       <c r="T61" s="178" t="n"/>
-      <c r="U61" s="179" t="n"/>
+      <c r="U61" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="52" customHeight="1">
       <c r="A62" s="152" t="inlineStr">
@@ -14265,10 +14898,14 @@
       </c>
       <c r="N62" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O62" s="178" t="n"/>
+          <t>@mint_minamoa_hiroshima</t>
+        </is>
+      </c>
+      <c r="O62" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mint_minamoa_hiroshima/</t>
+        </is>
+      </c>
       <c r="P62" s="180" t="inlineStr">
         <is>
           <t>https://img07.shop-pro.jp/PA01031/426/product/186260189.jpg?cmsp_timestamp=20250702151434</t>
@@ -14286,7 +14923,11 @@
         </is>
       </c>
       <c r="T62" s="178" t="n"/>
-      <c r="U62" s="179" t="n"/>
+      <c r="U62" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 표시명이 상호와 정확히 일치(지점 전용 계정), 프로필사진/바이오는 페이지에서 추출 안됨</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="52" customHeight="1">
       <c r="A63" s="152" t="inlineStr">
@@ -14512,12 +15153,24 @@
       </c>
       <c r="N65" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O65" s="178" t="n"/>
-      <c r="P65" s="178" t="n"/>
-      <c r="Q65" s="178" t="n"/>
+          <t>@mintcardjapan</t>
+        </is>
+      </c>
+      <c r="O65" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mintcardjapan/</t>
+        </is>
+      </c>
+      <c r="P65" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-19/604740660_18059372816642657_3350166706630106538_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=106&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy40MDAuQzMifQ%3D%3D&amp;_nc_ohc=7kNCEvzHHZ0Q7kNvwH0X5jm&amp;_nc_oc=AdqnWFt3A1Czngb6c4p3Ci0hbtbJ2W7qHvoJs52tn-b3OjjDI8m7yEK4RaQbJM0NU-E&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=gARWiqER6H87eYbxdJW3WQ&amp;_nc_ss=7fa02&amp;oh=00_AQK7roYcWw-fa3sBdcNy6lUAX9OTzU6PXvQONlnqAB6KwQ&amp;oe=6AAA0A2B</t>
+        </is>
+      </c>
+      <c r="Q65" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R65" s="178" t="n"/>
       <c r="S65" s="178" t="inlineStr">
         <is>
@@ -14525,7 +15178,11 @@
         </is>
       </c>
       <c r="T65" s="178" t="n"/>
-      <c r="U65" s="179" t="n"/>
+      <c r="U65" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 1번 후보는 동명 상업몰(고베 미나토미라이 ミント神戸)이라 거절, MINT 트레카 브랜드 공식 계정으로 대체</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="52" customHeight="1">
       <c r="A66" s="156" t="inlineStr">
@@ -14590,18 +15247,30 @@
       </c>
       <c r="N66" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O66" s="178" t="n"/>
-      <c r="P66" s="178" t="n"/>
-      <c r="Q66" s="178" t="n"/>
+          <t>@dorasutagram</t>
+        </is>
+      </c>
+      <c r="O66" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorasutagram/</t>
+        </is>
+      </c>
+      <c r="P66" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/254500530_2169236193232209_1218375009411615545_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=105&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy43NTYuQzMifQ%3D%3D&amp;_nc_ohc=xp-gt6Ohl74Q7kNvwHdo7xg&amp;_nc_oc=Adotp8f0urkbmBDGbBTZPKh-3HYm5MDL09SauYr490vFZxngTZDaUkML0fsR5eI2jZM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQK_9uRV0leFJTBKR7mKKCsS_A4KgiCd00jilCtqC9UAtw&amp;oe=6AAA1060</t>
+        </is>
+      </c>
+      <c r="Q66" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R66" s="178" t="n"/>
       <c r="S66" s="178" t="n"/>
       <c r="T66" s="178" t="n"/>
       <c r="U66" s="179" t="inlineStr">
         <is>
-          <t>공식 사이트/검색 모두 미확인</t>
+          <t>브랜드 공식 계정 ドラゴンスター 브랜드 공식 계정(전 지점 공용)</t>
         </is>
       </c>
     </row>
@@ -14668,12 +15337,24 @@
       </c>
       <c r="N67" s="178" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O67" s="178" t="n"/>
-      <c r="P67" s="178" t="n"/>
-      <c r="Q67" s="178" t="n"/>
+          <t>@hareruya2_pokeca</t>
+        </is>
+      </c>
+      <c r="O67" s="180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hareruya2_pokeca/</t>
+        </is>
+      </c>
+      <c r="P67" s="180" t="inlineStr">
+        <is>
+          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.2885-19/309447477_5776110002452355_8035051096901770384_n.jpg?stp=dst-jpg_s150x150_tt6&amp;_nc_cat=108&amp;ccb=7-5&amp;_nc_sid=f7ccc5&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLnd3dy4xMDAwLkMzIn0%3D&amp;_nc_ohc=ofjN7V1G6LQQ7kNvwFs4g0i&amp;_nc_oc=AdqDEK0i6u15GmgKXjitQHTMyQbQgIZGeTXdDX9uqte7483mUdvwAhb46cHd-6resFM&amp;_nc_zt=24&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_ss=7fa02&amp;oh=00_AQJtSGhFfuLKG9TvLKDgAzApF81t3mhHlfjZ1k2g2a4IFg&amp;oe=6AAA0FAB</t>
+        </is>
+      </c>
+      <c r="Q67" s="178" t="inlineStr">
+        <is>
+          <t>인스타 프로필(단기 만료)</t>
+        </is>
+      </c>
       <c r="R67" s="178" t="n"/>
       <c r="S67" s="178" t="inlineStr">
         <is>
@@ -14681,7 +15362,11 @@
         </is>
       </c>
       <c r="T67" s="178" t="n"/>
-      <c r="U67" s="179" t="n"/>
+      <c r="U67" s="179" t="inlineStr">
+        <is>
+          <t>브랜드 공식 계정 晴れる屋2 브랜드 공식 계정(전 지점 공용)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14689,43 +15374,114 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId105"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14736,7 +15492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15053,6 +15809,18 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2차 보강(2026-09-12)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>검색 첫 결과로 노출되는 인스타그램 계정을 추가 수집해 프로필(표시명·소개글·주소)로 대조 검증 후 반영. 한국 46곳·일본 43곳으로 확대. 일본 체인(ドラゴンスター·晴れる屋2·MINT·駿河屋·포켓몬센터)은 지점 전용 계정이 없어 브랜드 공식 계정을 넣고 비고에 표시. 무관 계정으로 판명된 후보는 채우지 않고 "없음" 유지.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
